--- a/templates/BNY11731 - template.xlsx
+++ b/templates/BNY11731 - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$44</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -811,15 +811,15 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1238,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="57" min="1" max="1"/>
@@ -1246,8 +1246,8 @@
     <col width="5.42578125" customWidth="1" style="57" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="57" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="57" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="57" min="10" max="19"/>
-    <col width="9.140625" customWidth="1" style="57" min="20" max="16384"/>
+    <col width="9.140625" customWidth="1" style="57" min="10" max="20"/>
+    <col width="9.140625" customWidth="1" style="57" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1399,96 +1399,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>1.0923566</v>
+        <v>1.08312095</v>
       </c>
       <c r="D18" s="31" t="n">
-        <v>-0.00561859648667018</v>
+        <v>-0.002390559774346879</v>
       </c>
       <c r="E18" s="31" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>-10.35376120082943</v>
+        <v>-4.405243391052798</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="34" t="n">
-        <v>1.09852879</v>
+        <v>1.08571642</v>
       </c>
       <c r="D19" s="35" t="n">
-        <v>-0.110815658542735</v>
+        <v>-0.00235244437367399</v>
       </c>
       <c r="E19" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>-204.2073796518721</v>
+        <v>-4.335005608792177</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>1.23543425</v>
+        <v>1.08827653</v>
       </c>
       <c r="D20" s="35" t="n">
-        <v>-0.001210035179165736</v>
+        <v>0.001688419381663087</v>
       </c>
       <c r="E20" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>-2.229812252830023</v>
+        <v>3.111362619840309</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="34" t="n">
-        <v>1.23693098</v>
+        <v>1.08644216</v>
       </c>
       <c r="D21" s="35" t="n">
-        <v>0.001375871692905095</v>
+        <v>-0.001720091558856329</v>
       </c>
       <c r="E21" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>2.535410219459049</v>
+        <v>-3.169727045929134</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>1.23523146</v>
+        <v>1.08831416</v>
       </c>
       <c r="D22" s="35" t="n">
-        <v>0.002532026884704885</v>
+        <v>0.003732113904912016</v>
       </c>
       <c r="E22" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>4.665934238294302</v>
+        <v>6.877414357380665</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1528,18 +1528,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B25" s="37" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr"/>
       <c r="D25" s="31" t="n">
-        <v>-0.1411812251077421</v>
+        <v>0.00876291698677889</v>
       </c>
       <c r="E25" s="31" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>-13.46716363513537</v>
+        <v>2.303105692433632</v>
       </c>
       <c r="G25" s="38" t="n"/>
     </row>
@@ -1552,13 +1552,13 @@
       </c>
       <c r="C26" s="40" t="inlineStr"/>
       <c r="D26" s="35" t="n">
-        <v>-0.1376974438707461</v>
+        <v>-0.1398292112352284</v>
       </c>
       <c r="E26" s="35" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="36" t="n">
-        <v>-11.87266465455209</v>
+        <v>-12.14805376948394</v>
       </c>
       <c r="G26" s="41" t="n"/>
       <c r="H26" s="42" t="n"/>
@@ -1572,13 +1572,13 @@
       </c>
       <c r="C27" s="40" t="inlineStr"/>
       <c r="D27" s="35" t="n">
-        <v>-0.2216194481675435</v>
+        <v>-0.2073405809490573</v>
       </c>
       <c r="E27" s="35" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="36" t="n">
-        <v>-6.280281766347738</v>
+        <v>-5.890582335780951</v>
       </c>
       <c r="G27" s="41" t="n"/>
     </row>
@@ -1591,13 +1591,13 @@
       </c>
       <c r="C28" s="40" t="inlineStr"/>
       <c r="D28" s="35" t="n">
-        <v>-0.2579287122402225</v>
+        <v>-0.2667779054067561</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="36" t="n">
-        <v>-3.588930361759648</v>
+        <v>-3.716853142539711</v>
       </c>
       <c r="G28" s="41" t="n"/>
     </row>
@@ -1610,13 +1610,13 @@
       </c>
       <c r="C29" s="40" t="inlineStr"/>
       <c r="D29" s="35" t="n">
-        <v>-0.2140404827684085</v>
+        <v>-0.2227557459617646</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F29" s="36" t="n">
-        <v>-1.448010471627826</v>
+        <v>-1.504943326319085</v>
       </c>
       <c r="G29" s="41" t="n"/>
     </row>
@@ -1624,18 +1624,18 @@
       <c r="A30" s="43" t="n"/>
       <c r="B30" s="40" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr"/>
       <c r="D30" s="35" t="n">
-        <v>-0.2128852432745275</v>
+        <v>-0.1613124745174513</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F30" s="36" t="n">
-        <v>-6.56262769764617</v>
+        <v>-0.580405865931918</v>
       </c>
       <c r="G30" s="41" t="n"/>
     </row>
@@ -1643,18 +1643,18 @@
       <c r="A31" s="43" t="n"/>
       <c r="B31" s="40" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C31" s="40" t="inlineStr"/>
       <c r="D31" s="35" t="n">
-        <v>0.03136788880013142</v>
+        <v>-0.2195401363771567</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F31" s="36" t="n">
-        <v>0.2191524200225768</v>
+        <v>-5.768963855418453</v>
       </c>
       <c r="G31" s="41" t="n"/>
     </row>
@@ -1662,172 +1662,191 @@
       <c r="A32" s="43" t="n"/>
       <c r="B32" s="40" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr"/>
       <c r="D32" s="35" t="n">
-        <v>0.08535468488664977</v>
+        <v>0.03136788880013142</v>
       </c>
       <c r="E32" s="35" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F32" s="36" t="n">
-        <v>0.781601047429532</v>
-      </c>
+        <v>0.2191524200225768</v>
+      </c>
+      <c r="G32" s="41" t="n"/>
     </row>
     <row r="33" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="A33" s="43" t="n"/>
       <c r="B33" s="40" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C33" s="40" t="inlineStr"/>
       <c r="D33" s="35" t="n">
-        <v>0.09235660000000001</v>
+        <v>0.08535468488664977</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>0.6102126585466485</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F33" s="36" t="n">
-        <v>0.1513514980498224</v>
-      </c>
-    </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="13" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="26.1" customHeight="1">
+        <v>0.781601047429532</v>
+      </c>
+    </row>
+    <row r="34" ht="15.95" customFormat="1" customHeight="1" s="28">
+      <c r="A34" s="43" t="n"/>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr"/>
+      <c r="D34" s="35" t="n">
+        <v>0.08312095000000008</v>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>0.6189720455365777</v>
+      </c>
+      <c r="F34" s="36" t="n">
+        <v>0.1342886978489372</v>
+      </c>
+    </row>
+    <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="13" t="n"/>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="26.1" customHeight="1">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="59" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customFormat="1" customHeight="1" s="28">
-      <c r="A36" s="48" t="n"/>
-      <c r="B36" s="49" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="E36" s="44" t="n">
-        <v>2431673.31</v>
-      </c>
-      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="A37" s="48" t="n"/>
-      <c r="B37" s="50" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="n">
+        <v>1911114.01</v>
+      </c>
+      <c r="F37" s="44" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customFormat="1" customHeight="1" s="28">
+      <c r="A38" s="48" t="n"/>
+      <c r="B38" s="50" t="inlineStr">
         <is>
           <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
-      <c r="E37" s="44" t="n">
-        <v>3789301.309563492</v>
-      </c>
-      <c r="F37" s="44" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="E38" s="44" t="n">
+        <v>3681854.835515874</v>
+      </c>
+      <c r="F38" s="44" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="17" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="15.95" customHeight="1">
-      <c r="B41" s="21" t="n"/>
-      <c r="C41" s="22" t="n"/>
       <c r="D41" s="20" t="n"/>
       <c r="E41" s="20" t="n"/>
       <c r="F41" s="20" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
-    <row r="42" ht="51.75" customHeight="1">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="58" t="inlineStr">
+    <row r="42" ht="15.95" customHeight="1">
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="51.75" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="58" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="59" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="23" t="n"/>
+      <c r="B44" s="56" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
       <c r="G45" s="4" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="4" t="n"/>
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="25" t="n"/>
       <c r="D46" s="12" t="n"/>
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
+      <c r="G46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="25" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="84" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="82"/>
 </worksheet>
 </file>